--- a/расчет_ступеней_по_высоте_лопаток.xlsx
+++ b/расчет_ступеней_по_высоте_лопаток.xlsx
@@ -650,1822 +650,1822 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119.7119096203353</v>
+        <v>119.0593945627731</v>
       </c>
       <c r="B2" t="n">
-        <v>128.318308583747</v>
+        <v>125.5263054044733</v>
       </c>
       <c r="C2" t="n">
-        <v>66.83868709831319</v>
+        <v>66.47436871179966</v>
       </c>
       <c r="D2" t="n">
-        <v>106.743581851173</v>
+        <v>106.1617534042214</v>
       </c>
       <c r="E2" t="n">
-        <v>65.31381077387752</v>
+        <v>65.02624980008299</v>
       </c>
       <c r="F2" t="n">
-        <v>227.9246854345401</v>
+        <v>226.6823337779018</v>
       </c>
       <c r="G2" t="n">
-        <v>299.2797740508382</v>
+        <v>297.6484864069328</v>
       </c>
       <c r="H2" t="n">
-        <v>230.254176372237</v>
+        <v>228.4200897566096</v>
       </c>
       <c r="I2" t="n">
-        <v>209.4958418355867</v>
+        <v>208.3539404848529</v>
       </c>
       <c r="J2" t="n">
-        <v>205.2560450365332</v>
+        <v>204.2116657156898</v>
       </c>
       <c r="K2" t="n">
-        <v>200.9064264774255</v>
+        <v>199.9576392616492</v>
       </c>
       <c r="L2" t="n">
-        <v>211.2564462394818</v>
+        <v>210.2652388345602</v>
       </c>
       <c r="M2" t="n">
         <v>1.261959540353609</v>
       </c>
       <c r="N2" t="n">
-        <v>1.091237004415033</v>
+        <v>1.091386175302926</v>
       </c>
       <c r="O2" t="n">
-        <v>1.256477893369617</v>
+        <v>1.256383429801283</v>
       </c>
       <c r="P2" t="n">
         <v>1.323575950546099</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.466069598564363</v>
+        <v>1.47625314095384</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1424936480182644</v>
+        <v>0.1526771904077411</v>
       </c>
       <c r="S2" t="n">
-        <v>0.165240888954584</v>
+        <v>0.1649972544983576</v>
       </c>
       <c r="T2" t="n">
-        <v>299.2797740508382</v>
+        <v>297.6484864069328</v>
       </c>
       <c r="U2" t="n">
-        <v>299.2797740508382</v>
+        <v>297.6484864069328</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="X2" t="n">
-        <v>66.83868709831319</v>
+        <v>66.47436871179966</v>
       </c>
       <c r="Y2" t="n">
-        <v>106.743581851173</v>
+        <v>106.1617534042214</v>
       </c>
       <c r="Z2" t="n">
-        <v>65.31381077387753</v>
+        <v>65.02624980008299</v>
       </c>
       <c r="AA2" t="n">
-        <v>209.4958418355867</v>
+        <v>208.3539404848529</v>
       </c>
       <c r="AB2" t="n">
-        <v>205.2560450365332</v>
+        <v>204.2116657156898</v>
       </c>
       <c r="AC2" t="n">
-        <v>200.9064264774255</v>
+        <v>199.9576392616492</v>
       </c>
       <c r="AD2" t="n">
-        <v>211.2564462394818</v>
+        <v>210.2652388345602</v>
       </c>
       <c r="AE2" t="n">
         <v>1.261959540353609</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.091237004415033</v>
+        <v>1.091386175302926</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.256477893369617</v>
+        <v>1.256383429801283</v>
       </c>
       <c r="AH2" t="n">
         <v>0.7335250127421162</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.8173633931624241</v>
+        <v>0.8175452455918298</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.08383838042030789</v>
+        <v>0.08402023284971361</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.165240888954584</v>
+        <v>0.1649972544983576</v>
       </c>
       <c r="AL2" t="n">
-        <v>312.9175077397755</v>
+        <v>311.2118847468536</v>
       </c>
       <c r="AM2" t="n">
-        <v>216.0650027335858</v>
+        <v>214.8872947833659</v>
       </c>
       <c r="AN2" t="n">
-        <v>281.4253530348425</v>
+        <v>279.9456613888279</v>
       </c>
       <c r="AO2" t="n">
-        <v>206.3868039813219</v>
+        <v>205.1277413919119</v>
       </c>
       <c r="AP2" t="n">
-        <v>324.9022810196093</v>
+        <v>325.0748661172555</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9631126834744798</v>
+        <v>0.957354496408832</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.006970718594023</v>
+        <v>1.001482011927405</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.8111271531740062</v>
+        <v>0.8067059332409005</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.6952986831487622</v>
+        <v>0.6915088107651657</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132.2133051489463</v>
+        <v>131.4904843997926</v>
       </c>
       <c r="B3" t="n">
-        <v>192.1397238059823</v>
+        <v>190.5185789858444</v>
       </c>
       <c r="C3" t="n">
-        <v>65.31381077387752</v>
+        <v>65.02624980008299</v>
       </c>
       <c r="D3" t="n">
-        <v>113.4643287194534</v>
+        <v>112.7750003300062</v>
       </c>
       <c r="E3" t="n">
-        <v>64.39360400214129</v>
+        <v>64.16911713233031</v>
       </c>
       <c r="F3" t="n">
-        <v>231.2475942211802</v>
+        <v>229.9841570038544</v>
       </c>
       <c r="G3" t="n">
-        <v>299.2797740508382</v>
+        <v>297.6484864069328</v>
       </c>
       <c r="H3" t="n">
-        <v>251.5217966400002</v>
+        <v>249.9325241001976</v>
       </c>
       <c r="I3" t="n">
-        <v>200.9064264774255</v>
+        <v>199.9576392616492</v>
       </c>
       <c r="J3" t="n">
-        <v>196.6689460182242</v>
+        <v>195.8176782206505</v>
       </c>
       <c r="K3" t="n">
-        <v>192.3262764786733</v>
+        <v>191.5705929511034</v>
       </c>
       <c r="L3" t="n">
-        <v>202.819951830523</v>
+        <v>202.0320956610114</v>
       </c>
       <c r="M3" t="n">
-        <v>1.256477893369617</v>
+        <v>1.256383429801283</v>
       </c>
       <c r="N3" t="n">
-        <v>1.047512376721574</v>
+        <v>1.048272132741518</v>
       </c>
       <c r="O3" t="n">
-        <v>1.247713418562088</v>
+        <v>1.247579524494355</v>
       </c>
       <c r="P3" t="n">
-        <v>1.249356312295982</v>
+        <v>1.249893594443205</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.19025568690558</v>
+        <v>1.19286135776193</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.05910062539040228</v>
+        <v>-0.05703223668127477</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2002010418405142</v>
+        <v>0.199307391752837</v>
       </c>
       <c r="T3" t="n">
-        <v>299.1162677083258</v>
+        <v>297.4822304909237</v>
       </c>
       <c r="U3" t="n">
-        <v>299.1162677083258</v>
+        <v>297.4822304909237</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="X3" t="n">
-        <v>65.31381077387753</v>
+        <v>65.02624980008299</v>
       </c>
       <c r="Y3" t="n">
-        <v>113.4643287194534</v>
+        <v>112.7750003300062</v>
       </c>
       <c r="Z3" t="n">
-        <v>64.39360400214127</v>
+        <v>64.1691171323303</v>
       </c>
       <c r="AA3" t="n">
-        <v>200.9064264774255</v>
+        <v>199.9576392616492</v>
       </c>
       <c r="AB3" t="n">
-        <v>196.6689460182242</v>
+        <v>195.8176782206505</v>
       </c>
       <c r="AC3" t="n">
-        <v>192.3262764786733</v>
+        <v>191.5705929511034</v>
       </c>
       <c r="AD3" t="n">
-        <v>202.819951830523</v>
+        <v>202.0320956610114</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.256477893369617</v>
+        <v>1.256383429801283</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.047512376721574</v>
+        <v>1.048272132741518</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.247713418562088</v>
+        <v>1.247579524494355</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.7098684159211058</v>
+        <v>0.7103835041928495</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.8142063179748668</v>
+        <v>0.8145875599160323</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1043379020537609</v>
+        <v>0.1042040557231828</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.2002010418405142</v>
+        <v>0.199307391752837</v>
       </c>
       <c r="AL3" t="n">
-        <v>308.264466113942</v>
+        <v>306.6249181949053</v>
       </c>
       <c r="AM3" t="n">
-        <v>211.7520591341889</v>
+        <v>210.7143848436007</v>
       </c>
       <c r="AN3" t="n">
-        <v>270.4539087871484</v>
+        <v>269.1864112050317</v>
       </c>
       <c r="AO3" t="n">
-        <v>211.8218405168376</v>
+        <v>210.6860866928396</v>
       </c>
       <c r="AP3" t="n">
-        <v>348.3256647459656</v>
+        <v>348.4528312601311</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.884989242290716</v>
+        <v>0.8799610469113969</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9335958304830705</v>
+        <v>0.9286303697525945</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.7535158999885552</v>
+        <v>0.7496030490848531</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.6413027164500107</v>
+        <v>0.6381600629898013</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>144.7009618648572</v>
+        <v>143.9076050082215</v>
       </c>
       <c r="B4" t="n">
-        <v>207.7332200693776</v>
+        <v>206.2308840189245</v>
       </c>
       <c r="C4" t="n">
-        <v>64.39360400214129</v>
+        <v>64.16911713233031</v>
       </c>
       <c r="D4" t="n">
-        <v>120.1023032925194</v>
+        <v>119.3161255839876</v>
       </c>
       <c r="E4" t="n">
-        <v>63.99525252066636</v>
+        <v>63.82422410637949</v>
       </c>
       <c r="F4" t="n">
-        <v>234.8522108612775</v>
+        <v>233.5660372535288</v>
       </c>
       <c r="G4" t="n">
-        <v>299.2797740508382</v>
+        <v>297.6484864069328</v>
       </c>
       <c r="H4" t="n">
-        <v>257.6974315478832</v>
+        <v>256.1454509652013</v>
       </c>
       <c r="I4" t="n">
-        <v>192.3262764786733</v>
+        <v>191.5705929511034</v>
       </c>
       <c r="J4" t="n">
-        <v>188.0911123593243</v>
+        <v>187.4329456382691</v>
       </c>
       <c r="K4" t="n">
-        <v>183.7553918393301</v>
+        <v>183.1928015532153</v>
       </c>
       <c r="L4" t="n">
-        <v>194.5801541144667</v>
+        <v>193.9926135802523</v>
       </c>
       <c r="M4" t="n">
-        <v>1.247713418562088</v>
+        <v>1.247579524494355</v>
       </c>
       <c r="N4" t="n">
-        <v>1.002524847928268</v>
+        <v>1.003912892576705</v>
       </c>
       <c r="O4" t="n">
-        <v>1.235669548124329</v>
+        <v>1.235548327881696</v>
       </c>
       <c r="P4" t="n">
-        <v>1.175246045654814</v>
+        <v>1.176372619761417</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.134802113664447</v>
+        <v>1.136598838224037</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.04044393199036711</v>
+        <v>-0.03977378153737932</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2331447001960611</v>
+        <v>0.2316354353049905</v>
       </c>
       <c r="T4" t="n">
-        <v>298.9527613658134</v>
+        <v>297.3159745749147</v>
       </c>
       <c r="U4" t="n">
-        <v>298.9527613658134</v>
+        <v>297.3159745749147</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="X4" t="n">
-        <v>64.39360400214127</v>
+        <v>64.1691171323303</v>
       </c>
       <c r="Y4" t="n">
-        <v>120.1023032925194</v>
+        <v>119.3161255839876</v>
       </c>
       <c r="Z4" t="n">
-        <v>63.99525252066638</v>
+        <v>63.82422410637949</v>
       </c>
       <c r="AA4" t="n">
-        <v>192.3262764786733</v>
+        <v>191.5705929511034</v>
       </c>
       <c r="AB4" t="n">
-        <v>188.0911123593243</v>
+        <v>187.4329456382691</v>
       </c>
       <c r="AC4" t="n">
-        <v>183.7553918393301</v>
+        <v>183.1928015532153</v>
       </c>
       <c r="AD4" t="n">
-        <v>194.5801541144667</v>
+        <v>193.9926135802523</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.247713418562088</v>
+        <v>1.247579524494355</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.002524847928268</v>
+        <v>1.003912892576705</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.235669548124329</v>
+        <v>1.235548327881696</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.6867864654664104</v>
+        <v>0.6878174831269123</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.8105757457835095</v>
+        <v>0.8112059245454323</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.1237892803170991</v>
+        <v>0.12338844141852</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.2331447001960611</v>
+        <v>0.2316354353049905</v>
       </c>
       <c r="AL4" t="n">
-        <v>303.3272076937824</v>
+        <v>301.7561088345853</v>
       </c>
       <c r="AM4" t="n">
-        <v>208.4194529093708</v>
+        <v>207.5030566819944</v>
       </c>
       <c r="AN4" t="n">
-        <v>259.5491338871988</v>
+        <v>258.4860834772952</v>
       </c>
       <c r="AO4" t="n">
-        <v>207.5028773866054</v>
+        <v>206.6041731050992</v>
       </c>
       <c r="AP4" t="n">
-        <v>370.1897845951318</v>
+        <v>370.2807673122638</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.8193829768304507</v>
+        <v>0.8149386505405762</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.8702616009170909</v>
+        <v>0.8657540362353754</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.7048918265340827</v>
+        <v>0.7014089364071879</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.5979662956390018</v>
+        <v>0.595337107001509</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>157.174879768068</v>
+        <v>156.3107563880597</v>
       </c>
       <c r="B5" t="n">
-        <v>216.931332533211</v>
+        <v>215.4612694674828</v>
       </c>
       <c r="C5" t="n">
-        <v>63.99525252066636</v>
+        <v>63.82422410637949</v>
       </c>
       <c r="D5" t="n">
-        <v>126.7394540178891</v>
+        <v>125.8629954717696</v>
       </c>
       <c r="E5" t="n">
-        <v>64.06178548213539</v>
+        <v>63.93702943947437</v>
       </c>
       <c r="F5" t="n">
-        <v>238.7246968240675</v>
+        <v>237.4142033047667</v>
       </c>
       <c r="G5" t="n">
-        <v>299.2797740508382</v>
+        <v>297.6484864069328</v>
       </c>
       <c r="H5" t="n">
-        <v>261.5169460780244</v>
+        <v>259.9751482238725</v>
       </c>
       <c r="I5" t="n">
-        <v>183.7553918393301</v>
+        <v>183.1928015532153</v>
       </c>
       <c r="J5" t="n">
-        <v>179.5225440598334</v>
+        <v>179.0574679685456</v>
       </c>
       <c r="K5" t="n">
-        <v>175.193772559396</v>
+        <v>174.8242650679852</v>
       </c>
       <c r="L5" t="n">
-        <v>186.5389243636633</v>
+        <v>186.1490461702808</v>
       </c>
       <c r="M5" t="n">
-        <v>1.235669548124329</v>
+        <v>1.235548327881696</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9560677274732393</v>
+        <v>0.9581136167675917</v>
       </c>
       <c r="O5" t="n">
-        <v>1.220237018685182</v>
+        <v>1.220184754382479</v>
       </c>
       <c r="P5" t="n">
-        <v>1.101496690170982</v>
+        <v>1.103269087847205</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.105231662921588</v>
+        <v>1.106838072462835</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003734972750605747</v>
+        <v>0.003568984615629711</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2641692912119423</v>
+        <v>0.2620711376148872</v>
       </c>
       <c r="T5" t="n">
-        <v>298.7892550233011</v>
+        <v>297.1497186589057</v>
       </c>
       <c r="U5" t="n">
-        <v>298.7892550233011</v>
+        <v>297.1497186589057</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="X5" t="n">
-        <v>63.99525252066638</v>
+        <v>63.82422410637949</v>
       </c>
       <c r="Y5" t="n">
-        <v>126.7394540178891</v>
+        <v>125.8629954717696</v>
       </c>
       <c r="Z5" t="n">
-        <v>64.06178548213539</v>
+        <v>63.93702943947435</v>
       </c>
       <c r="AA5" t="n">
-        <v>183.7553918393301</v>
+        <v>183.1928015532153</v>
       </c>
       <c r="AB5" t="n">
-        <v>179.5225440598334</v>
+        <v>179.0574679685456</v>
       </c>
       <c r="AC5" t="n">
-        <v>175.193772559396</v>
+        <v>174.8242650679852</v>
       </c>
       <c r="AD5" t="n">
-        <v>186.5389243636633</v>
+        <v>186.1490461702808</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.235669548124329</v>
+        <v>1.235548327881696</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.9560677274732393</v>
+        <v>0.9581136167675918</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.220237018685182</v>
+        <v>1.220184754382479</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.6640555758472819</v>
+        <v>0.665613059220287</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.8066501705857518</v>
+        <v>0.807574842898458</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.1425945947384699</v>
+        <v>0.141961783678171</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.2641692912119423</v>
+        <v>0.2620711376148871</v>
       </c>
       <c r="AL5" t="n">
-        <v>298.1514173054238</v>
+        <v>296.6485950566708</v>
       </c>
       <c r="AM5" t="n">
-        <v>206.0303059357785</v>
+        <v>205.2154019424614</v>
       </c>
       <c r="AN5" t="n">
-        <v>248.6553394796031</v>
+        <v>247.7916834268117</v>
       </c>
       <c r="AO5" t="n">
-        <v>200.905248253592</v>
+        <v>200.2234440277102</v>
       </c>
       <c r="AP5" t="n">
-        <v>390.7647231244763</v>
+        <v>390.8263045194765</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.7629947118088473</v>
+        <v>0.7590292455401696</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.8146563830034048</v>
+        <v>0.8105501347469626</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.6632870776470119</v>
+        <v>0.6601667009204055</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.5629485358132251</v>
+        <v>0.5607219264424214</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>169.6350588585787</v>
+        <v>168.6999385393073</v>
       </c>
       <c r="B6" t="n">
-        <v>224.1077944280078</v>
+        <v>222.6439190024189</v>
       </c>
       <c r="C6" t="n">
-        <v>64.06178548213539</v>
+        <v>63.93702943947437</v>
       </c>
       <c r="D6" t="n">
-        <v>133.4318859279603</v>
+        <v>132.469270979551</v>
       </c>
       <c r="E6" t="n">
-        <v>64.5545645333364</v>
+        <v>64.46970880293171</v>
       </c>
       <c r="F6" t="n">
-        <v>242.8511797059209</v>
+        <v>241.5148508952685</v>
       </c>
       <c r="G6" t="n">
-        <v>299.2797740508382</v>
+        <v>297.6484864069328</v>
       </c>
       <c r="H6" t="n">
-        <v>264.5873407796041</v>
+        <v>263.0467510666629</v>
       </c>
       <c r="I6" t="n">
-        <v>175.193772559396</v>
+        <v>174.8242650679852</v>
       </c>
       <c r="J6" t="n">
-        <v>170.9632411197515</v>
+        <v>170.6912452114798</v>
       </c>
       <c r="K6" t="n">
-        <v>166.641418638871</v>
+        <v>166.4649834954128</v>
       </c>
       <c r="L6" t="n">
-        <v>178.7082936185787</v>
+        <v>178.5131201992248</v>
       </c>
       <c r="M6" t="n">
-        <v>1.220237018685182</v>
+        <v>1.220184754382479</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9080771380395368</v>
+        <v>0.9108147654953038</v>
       </c>
       <c r="O6" t="n">
-        <v>1.201211096511818</v>
+        <v>1.201297323232269</v>
       </c>
       <c r="P6" t="n">
-        <v>1.028460948189159</v>
+        <v>1.030930717528527</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.083139188870513</v>
+        <v>1.084772911518393</v>
       </c>
       <c r="R6" t="n">
-        <v>0.05467824068135418</v>
+        <v>0.05384219398986656</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2931339584722811</v>
+        <v>0.2904825577369647</v>
       </c>
       <c r="T6" t="n">
-        <v>298.6257486807887</v>
+        <v>296.9834627428966</v>
       </c>
       <c r="U6" t="n">
-        <v>298.6257486807887</v>
+        <v>296.9834627428966</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="X6" t="n">
-        <v>64.06178548213539</v>
+        <v>63.93702943947435</v>
       </c>
       <c r="Y6" t="n">
-        <v>133.4318859279603</v>
+        <v>132.4692709795509</v>
       </c>
       <c r="Z6" t="n">
-        <v>64.5545645333364</v>
+        <v>64.46970880293171</v>
       </c>
       <c r="AA6" t="n">
-        <v>175.193772559396</v>
+        <v>174.8242650679852</v>
       </c>
       <c r="AB6" t="n">
-        <v>170.9632411197515</v>
+        <v>170.6912452114798</v>
       </c>
       <c r="AC6" t="n">
-        <v>166.641418638871</v>
+        <v>166.4649834954128</v>
       </c>
       <c r="AD6" t="n">
-        <v>178.7082936185787</v>
+        <v>178.5131201992248</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.220237018685182</v>
+        <v>1.220184754382479</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.9080771380395368</v>
+        <v>0.9108147654953039</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.201211096511818</v>
+        <v>1.201297323232269</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.6415085405234026</v>
+        <v>0.6436094117057235</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.80255922269068</v>
+        <v>0.8038237427897025</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.1610506821672775</v>
+        <v>0.160214331083979</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.2931339584722811</v>
+        <v>0.2904825577369646</v>
       </c>
       <c r="AL6" t="n">
-        <v>292.7680152869377</v>
+        <v>291.3317073921195</v>
       </c>
       <c r="AM6" t="n">
-        <v>204.544797037252</v>
+        <v>203.8106738608677</v>
       </c>
       <c r="AN6" t="n">
-        <v>237.733973393309</v>
+        <v>237.0662786720043</v>
       </c>
       <c r="AO6" t="n">
-        <v>193.5214463476317</v>
+        <v>193.046544485763</v>
       </c>
       <c r="AP6" t="n">
-        <v>410.2498663632237</v>
+        <v>410.2872663700887</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.7136334202427969</v>
+        <v>0.7100676313198848</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.7651514237334944</v>
+        <v>0.761397622179856</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.6273179841520936</v>
+        <v>0.6245014132134756</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.5345793751306509</v>
+        <v>0.5326607386530438</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>182.0814991363893</v>
+        <v>181.0751514619643</v>
       </c>
       <c r="B7" t="n">
-        <v>230.4468147033298</v>
+        <v>228.9779739498636</v>
       </c>
       <c r="C7" t="n">
-        <v>64.5545645333364</v>
+        <v>64.46970880293171</v>
       </c>
       <c r="D7" t="n">
-        <v>140.2173715610254</v>
+        <v>139.1718961394571</v>
       </c>
       <c r="E7" t="n">
-        <v>65.4572361267564</v>
+        <v>65.40509659637141</v>
       </c>
       <c r="F7" t="n">
-        <v>247.2179022940561</v>
+        <v>245.8542909382392</v>
       </c>
       <c r="G7" t="n">
-        <v>299.2797740508382</v>
+        <v>297.6484864069328</v>
       </c>
       <c r="H7" t="n">
-        <v>267.3625298640812</v>
+        <v>265.8191358725923</v>
       </c>
       <c r="I7" t="n">
-        <v>166.641418638871</v>
+        <v>166.4649834954128</v>
       </c>
       <c r="J7" t="n">
-        <v>162.4132035390787</v>
+        <v>162.3342773670719</v>
       </c>
       <c r="K7" t="n">
-        <v>158.0983300777549</v>
+        <v>158.1149568354982</v>
       </c>
       <c r="L7" t="n">
-        <v>171.1132132090584</v>
+        <v>171.1086386944626</v>
       </c>
       <c r="M7" t="n">
-        <v>1.201211096511818</v>
+        <v>1.201297323232269</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8586100699066463</v>
+        <v>0.8620698154219553</v>
       </c>
       <c r="O7" t="n">
-        <v>1.178255099026218</v>
+        <v>1.178573809730572</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9565432363251244</v>
+        <v>0.9597480817883586</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.063698360555587</v>
+        <v>1.065486625197959</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1071551242304626</v>
+        <v>0.1057385434096001</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3196450291195714</v>
+        <v>0.3165039943086163</v>
       </c>
       <c r="T7" t="n">
-        <v>298.4622423382763</v>
+        <v>296.8172068268876</v>
       </c>
       <c r="U7" t="n">
-        <v>298.4622423382763</v>
+        <v>296.8172068268876</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="X7" t="n">
-        <v>64.5545645333364</v>
+        <v>64.46970880293171</v>
       </c>
       <c r="Y7" t="n">
-        <v>140.2173715610255</v>
+        <v>139.1718961394571</v>
       </c>
       <c r="Z7" t="n">
-        <v>65.45723612675638</v>
+        <v>65.40509659637139</v>
       </c>
       <c r="AA7" t="n">
-        <v>166.641418638871</v>
+        <v>166.4649834954128</v>
       </c>
       <c r="AB7" t="n">
-        <v>162.4132035390787</v>
+        <v>162.3342773670719</v>
       </c>
       <c r="AC7" t="n">
-        <v>158.0983300777549</v>
+        <v>158.1149568354982</v>
       </c>
       <c r="AD7" t="n">
-        <v>171.1132132090584</v>
+        <v>171.1086386944626</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.201211096511818</v>
+        <v>1.201297323232269</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.8586100699066462</v>
+        <v>0.8620698154219553</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.178255099026218</v>
+        <v>1.178573809730572</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.6190155730352872</v>
+        <v>0.6216800427117836</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.7983967382921272</v>
+        <v>0.8000510702207504</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.17938116525684</v>
+        <v>0.1783710275089668</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.3196450291195715</v>
+        <v>0.3165039943086163</v>
       </c>
       <c r="AL7" t="n">
-        <v>287.1970824052275</v>
+        <v>285.8250348869396</v>
       </c>
       <c r="AM7" t="n">
-        <v>203.9165092952646</v>
+        <v>203.2422691957483</v>
       </c>
       <c r="AN7" t="n">
-        <v>226.7586554271634</v>
+        <v>226.2840285791862</v>
       </c>
       <c r="AO7" t="n">
-        <v>185.7939748581652</v>
+        <v>185.5196734041385</v>
       </c>
       <c r="AP7" t="n">
-        <v>428.7973610820337</v>
+        <v>428.8147766893407</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.6697734372257098</v>
+        <v>0.6665466080568594</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.7205570404062709</v>
+        <v>0.717114670829273</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.5959739916481565</v>
+        <v>0.593411001996268</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.5116120094160789</v>
+        <v>0.5099203889909618</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>194.5142006014998</v>
+        <v>193.4363951560307</v>
       </c>
       <c r="B8" t="n">
-        <v>236.3967509870175</v>
+        <v>234.9175024961589</v>
       </c>
       <c r="C8" t="n">
-        <v>65.4572361267564</v>
+        <v>65.40509659637141</v>
       </c>
       <c r="D8" t="n">
-        <v>147.1113986496777</v>
+        <v>145.9871562553104</v>
       </c>
       <c r="E8" t="n">
-        <v>66.77859375524145</v>
+        <v>66.7495525627096</v>
       </c>
       <c r="F8" t="n">
-        <v>251.81134816794</v>
+        <v>250.4190744005821</v>
       </c>
       <c r="G8" t="n">
-        <v>299.2797740508382</v>
+        <v>297.6484864069328</v>
       </c>
       <c r="H8" t="n">
-        <v>270.0185065157026</v>
+        <v>268.470317947798</v>
       </c>
       <c r="I8" t="n">
-        <v>158.0983300777549</v>
+        <v>158.1149568354982</v>
       </c>
       <c r="J8" t="n">
-        <v>153.8724313178149</v>
+        <v>153.9865644353219</v>
       </c>
       <c r="K8" t="n">
-        <v>149.5645068760478</v>
+        <v>149.7741850882416</v>
       </c>
       <c r="L8" t="n">
-        <v>163.795367153662</v>
+        <v>163.9750264100261</v>
       </c>
       <c r="M8" t="n">
-        <v>1.178255099026218</v>
+        <v>1.178573809730572</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8078574956047333</v>
+        <v>0.8120588747510585</v>
       </c>
       <c r="O8" t="n">
-        <v>1.150867730999436</v>
+        <v>1.151550779267621</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8861901581273175</v>
+        <v>0.8901472122914128</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.045021234169908</v>
+        <v>1.047070138029247</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1588310760425908</v>
+        <v>0.1569229257378341</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3430102353947029</v>
+        <v>0.3394919045165629</v>
       </c>
       <c r="T8" t="n">
-        <v>298.2987359957639</v>
+        <v>296.6509509108786</v>
       </c>
       <c r="U8" t="n">
-        <v>298.2987359957639</v>
+        <v>296.6509509108786</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="X8" t="n">
-        <v>65.45723612675638</v>
+        <v>65.40509659637139</v>
       </c>
       <c r="Y8" t="n">
-        <v>147.1113986496777</v>
+        <v>145.9871562553104</v>
       </c>
       <c r="Z8" t="n">
-        <v>66.77859375524145</v>
+        <v>66.74955256270961</v>
       </c>
       <c r="AA8" t="n">
-        <v>158.0983300777549</v>
+        <v>158.1149568354982</v>
       </c>
       <c r="AB8" t="n">
-        <v>153.8724313178149</v>
+        <v>153.9865644353219</v>
       </c>
       <c r="AC8" t="n">
-        <v>149.5645068760478</v>
+        <v>149.7741850882416</v>
       </c>
       <c r="AD8" t="n">
-        <v>163.795367153662</v>
+        <v>163.9750264100262</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.178255099026218</v>
+        <v>1.178573809730572</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.8078574956047332</v>
+        <v>0.8120588747510585</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.150867730999436</v>
+        <v>1.151550779267621</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.5964894510399338</v>
+        <v>0.5997382465130822</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.7941997980612135</v>
+        <v>0.7963045612803844</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.1977103470212798</v>
+        <v>0.1965663147673022</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.343010235394703</v>
+        <v>0.3394919045165626</v>
       </c>
       <c r="AL8" t="n">
-        <v>281.4431488500365</v>
+        <v>280.1338692709929</v>
       </c>
       <c r="AM8" t="n">
-        <v>204.0852323241687</v>
+        <v>203.4511071141273</v>
       </c>
       <c r="AN8" t="n">
-        <v>215.7181867470959</v>
+        <v>215.433147511261</v>
       </c>
       <c r="AO8" t="n">
-        <v>177.9005319319157</v>
+        <v>177.8214512062893</v>
       </c>
       <c r="AP8" t="n">
-        <v>446.5260640526525</v>
+        <v>446.5270171452865</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.6302950074082346</v>
+        <v>0.6273615224044679</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.6799600520047653</v>
+        <v>0.6767968632247476</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.568474141903633</v>
+        <v>0.5661239033110056</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.4930651385601436</v>
+        <v>0.4915331069134005</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>206.9331632539101</v>
+        <v>205.7836696215064</v>
       </c>
       <c r="B9" t="n">
-        <v>242.1296546595054</v>
+        <v>240.637830485891</v>
       </c>
       <c r="C9" t="n">
-        <v>66.77859375524145</v>
+        <v>66.7495525627096</v>
       </c>
       <c r="D9" t="n">
-        <v>154.1043078861514</v>
+        <v>152.9078112876369</v>
       </c>
       <c r="E9" t="n">
-        <v>68.54612603193664</v>
+        <v>68.52651927997881</v>
       </c>
       <c r="F9" t="n">
-        <v>256.6183442533546</v>
+        <v>255.1960942580177</v>
       </c>
       <c r="G9" t="n">
-        <v>299.2797740508382</v>
+        <v>297.6484864069328</v>
       </c>
       <c r="H9" t="n">
-        <v>272.6225912127578</v>
+        <v>271.0688846423778</v>
       </c>
       <c r="I9" t="n">
-        <v>149.5645068760478</v>
+        <v>149.7741850882416</v>
       </c>
       <c r="J9" t="n">
-        <v>145.3409244559601</v>
+        <v>145.6481064162296</v>
       </c>
       <c r="K9" t="n">
-        <v>141.0399490337499</v>
+        <v>141.4426682536428</v>
       </c>
       <c r="L9" t="n">
-        <v>156.8146632730144</v>
+        <v>157.1684200064992</v>
       </c>
       <c r="M9" t="n">
-        <v>1.150867730999436</v>
+        <v>1.151550779267621</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7561411176018422</v>
+        <v>0.7610868899281044</v>
       </c>
       <c r="O9" t="n">
-        <v>1.118407237987454</v>
+        <v>1.119639478507843</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8178662724338445</v>
+        <v>0.8225685674172102</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.026234701851356</v>
+        <v>1.028656307632515</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2083684294175111</v>
+        <v>0.2060877402153048</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3622661203856115</v>
+        <v>0.3585525885797388</v>
       </c>
       <c r="T9" t="n">
-        <v>298.1352296532515</v>
+        <v>296.4846949948695</v>
       </c>
       <c r="U9" t="n">
-        <v>298.1352296532515</v>
+        <v>296.4846949948695</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="X9" t="n">
-        <v>66.77859375524145</v>
+        <v>66.74955256270961</v>
       </c>
       <c r="Y9" t="n">
-        <v>154.1043078861514</v>
+        <v>152.9078112876369</v>
       </c>
       <c r="Z9" t="n">
-        <v>68.54612603193664</v>
+        <v>68.52651927997883</v>
       </c>
       <c r="AA9" t="n">
-        <v>149.5645068760478</v>
+        <v>149.7741850882416</v>
       </c>
       <c r="AB9" t="n">
-        <v>145.3409244559601</v>
+        <v>145.6481064162296</v>
       </c>
       <c r="AC9" t="n">
-        <v>141.0399490337499</v>
+        <v>141.4426682536428</v>
       </c>
       <c r="AD9" t="n">
-        <v>156.8146632730144</v>
+        <v>157.1684200064992</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.150867730999436</v>
+        <v>1.151550779267621</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.7561411176018422</v>
+        <v>0.7610868899281044</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.118407237987454</v>
+        <v>1.119639478507843</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.5738877874615661</v>
+        <v>0.5777398127966437</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.7899251889422564</v>
+        <v>0.7925593264156723</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.2160374014806903</v>
+        <v>0.2148195136190286</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.3622661203856115</v>
+        <v>0.3585525885797388</v>
       </c>
       <c r="AL9" t="n">
-        <v>275.4912606438175</v>
+        <v>274.2454050429499</v>
       </c>
       <c r="AM9" t="n">
-        <v>204.9703516814871</v>
+        <v>204.3594681563985</v>
       </c>
       <c r="AN9" t="n">
-        <v>204.6188914709334</v>
+        <v>204.518195859717</v>
       </c>
       <c r="AO9" t="n">
-        <v>169.9189394866927</v>
+        <v>170.0291950553181</v>
       </c>
       <c r="AP9" t="n">
-        <v>463.5305786944816</v>
+        <v>463.5181512332267</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.5943324417123234</v>
+        <v>0.5916605516165836</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.6426232418287757</v>
+        <v>0.6397171033065989</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.5441787372309846</v>
+        <v>0.5420113295911972</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.4781230140241747</v>
+        <v>0.4766980397786948</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>219.3383870936204</v>
+        <v>218.1169748583916</v>
       </c>
       <c r="B10" t="n">
-        <v>247.7252952947244</v>
+        <v>246.2210206820629</v>
       </c>
       <c r="C10" t="n">
-        <v>68.54612603193664</v>
+        <v>68.52651927997881</v>
       </c>
       <c r="D10" t="n">
-        <v>161.1677448423818</v>
+        <v>159.9095383618466</v>
       </c>
       <c r="E10" t="n">
-        <v>70.8102658920895</v>
+        <v>70.78076949317392</v>
       </c>
       <c r="F10" t="n">
-        <v>261.6261416082141</v>
+        <v>260.1726658005301</v>
       </c>
       <c r="G10" t="n">
-        <v>299.2797740508382</v>
+        <v>297.6484864069328</v>
       </c>
       <c r="H10" t="n">
-        <v>275.20554007802</v>
+        <v>273.6465527544992</v>
       </c>
       <c r="I10" t="n">
-        <v>141.0399490337499</v>
+        <v>141.4426682536428</v>
       </c>
       <c r="J10" t="n">
-        <v>136.8186829535144</v>
+        <v>137.3189033097953</v>
       </c>
       <c r="K10" t="n">
-        <v>132.5246565508609</v>
+        <v>133.1204063317017</v>
       </c>
       <c r="L10" t="n">
-        <v>150.2560426393297</v>
+        <v>150.7679008010763</v>
       </c>
       <c r="M10" t="n">
-        <v>1.118407237987454</v>
+        <v>1.119639478507843</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7038673149178016</v>
+        <v>0.7095397237824457</v>
       </c>
       <c r="O10" t="n">
-        <v>1.080072960617716</v>
+        <v>1.082107685762169</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7519930631944379</v>
+        <v>0.7574093917917258</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.006718912006519</v>
+        <v>1.009649915455992</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2547258488120806</v>
+        <v>0.2522405236642659</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3762056456999139</v>
+        <v>0.3725679619797233</v>
       </c>
       <c r="T10" t="n">
-        <v>297.9717233107392</v>
+        <v>296.3184390788605</v>
       </c>
       <c r="U10" t="n">
-        <v>297.9717233107392</v>
+        <v>296.3184390788605</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="X10" t="n">
-        <v>68.54612603193664</v>
+        <v>68.52651927997883</v>
       </c>
       <c r="Y10" t="n">
-        <v>161.1677448423819</v>
+        <v>159.9095383618466</v>
       </c>
       <c r="Z10" t="n">
-        <v>70.81026589208952</v>
+        <v>70.78076949317391</v>
       </c>
       <c r="AA10" t="n">
-        <v>141.0399490337499</v>
+        <v>141.4426682536428</v>
       </c>
       <c r="AB10" t="n">
-        <v>136.8186829535144</v>
+        <v>137.3189033097953</v>
       </c>
       <c r="AC10" t="n">
-        <v>132.5246565508609</v>
+        <v>133.1204063317017</v>
       </c>
       <c r="AD10" t="n">
-        <v>150.2560426393297</v>
+        <v>150.7679008010763</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.118407237987454</v>
+        <v>1.119639478507843</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.7038673149178015</v>
+        <v>0.7095397237824457</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.080072960617716</v>
+        <v>1.082107685762169</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.5511963329600934</v>
+        <v>0.5556666848313293</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.7854519034095749</v>
+        <v>0.788722631087308</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.2342555704494815</v>
+        <v>0.2330559462559787</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.376205645699914</v>
+        <v>0.3725679619797235</v>
       </c>
       <c r="AL10" t="n">
-        <v>269.3109205178618</v>
+        <v>268.1327789144218</v>
       </c>
       <c r="AM10" t="n">
-        <v>206.4717249880423</v>
+        <v>205.8721273093255</v>
       </c>
       <c r="AN10" t="n">
-        <v>193.4804396571009</v>
+        <v>193.5558560236013</v>
       </c>
       <c r="AO10" t="n">
-        <v>161.89985035646</v>
+        <v>162.1917173795194</v>
       </c>
       <c r="AP10" t="n">
-        <v>479.8876381159671</v>
+        <v>479.864640132048</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.5611957865286406</v>
+        <v>0.558767528360993</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.6079372777995632</v>
+        <v>0.6052777636666775</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.5225512567838405</v>
+        <v>0.520549355688999</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.4660852897849174</v>
+        <v>0.4647317695493731</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>231.7298721206305</v>
+        <v>230.4363108666861</v>
       </c>
       <c r="B11" t="n">
-        <v>253.2176482624485</v>
+        <v>251.7031296269704</v>
       </c>
       <c r="C11" t="n">
-        <v>70.8102658920895</v>
+        <v>70.78076949317392</v>
       </c>
       <c r="D11" t="n">
-        <v>168.2504107682017</v>
+        <v>166.9466844363867</v>
       </c>
       <c r="E11" t="n">
-        <v>73.64255457728426</v>
+        <v>73.57655425741854</v>
       </c>
       <c r="F11" t="n">
-        <v>266.8224763085357</v>
+        <v>265.3365871473167</v>
       </c>
       <c r="G11" t="n">
-        <v>299.2797740508382</v>
+        <v>297.6484864069328</v>
       </c>
       <c r="H11" t="n">
-        <v>277.7793991113805</v>
+        <v>276.216308950761</v>
       </c>
       <c r="I11" t="n">
-        <v>132.5246565508609</v>
+        <v>133.1204063317017</v>
       </c>
       <c r="J11" t="n">
-        <v>128.3057068104777</v>
+        <v>128.9989551160187</v>
       </c>
       <c r="K11" t="n">
-        <v>124.018629427381</v>
+        <v>124.8073993224185</v>
       </c>
       <c r="L11" t="n">
-        <v>144.2353850125355</v>
+        <v>144.8806276284738</v>
       </c>
       <c r="M11" t="n">
-        <v>1.080072960617716</v>
+        <v>1.082107685762169</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6515087310766435</v>
+        <v>0.6578687233789857</v>
       </c>
       <c r="O11" t="n">
-        <v>1.034946378902684</v>
+        <v>1.038117776037218</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6889341190739982</v>
+        <v>0.6950122037897969</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9858750800303991</v>
+        <v>0.9894935498590219</v>
       </c>
       <c r="R11" t="n">
-        <v>0.296940960956401</v>
+        <v>0.294481346069225</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3834376478260401</v>
+        <v>0.3802490526582323</v>
       </c>
       <c r="T11" t="n">
-        <v>297.8082169682268</v>
+        <v>296.1521831628515</v>
       </c>
       <c r="U11" t="n">
-        <v>297.8082169682268</v>
+        <v>296.1521831628515</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="X11" t="n">
-        <v>70.81026589208952</v>
+        <v>70.78076949317391</v>
       </c>
       <c r="Y11" t="n">
-        <v>168.2504107682016</v>
+        <v>166.9466844363867</v>
       </c>
       <c r="Z11" t="n">
-        <v>73.64255457728426</v>
+        <v>73.57655425741855</v>
       </c>
       <c r="AA11" t="n">
-        <v>132.5246565508609</v>
+        <v>133.1204063317017</v>
       </c>
       <c r="AB11" t="n">
-        <v>128.3057068104777</v>
+        <v>128.9989551160187</v>
       </c>
       <c r="AC11" t="n">
-        <v>124.018629427381</v>
+        <v>124.8073993224185</v>
       </c>
       <c r="AD11" t="n">
-        <v>144.2353850125355</v>
+        <v>144.8806276284738</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.080072960617716</v>
+        <v>1.082107685762169</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.6515087310766435</v>
+        <v>0.6578687233789857</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.034946378902684</v>
+        <v>1.038117776037218</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.528433251086966</v>
+        <v>0.5335318596194893</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.7805425344074856</v>
+        <v>0.7845982408425958</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.2521092833205195</v>
+        <v>0.2510663812231064</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.3834376478260401</v>
+        <v>0.3802490526582321</v>
       </c>
       <c r="AL11" t="n">
-        <v>262.8513922099102</v>
+        <v>261.7504855418348</v>
       </c>
       <c r="AM11" t="n">
-        <v>208.4655949135789</v>
+        <v>207.872399498314</v>
       </c>
       <c r="AN11" t="n">
-        <v>182.3391881837241</v>
+        <v>182.5781786582918</v>
       </c>
       <c r="AO11" t="n">
-        <v>153.8888749960178</v>
+        <v>154.3514995792689</v>
       </c>
       <c r="AP11" t="n">
-        <v>495.6601291350416</v>
+        <v>495.629228611946</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.5303057009418986</v>
+        <v>0.5281175330899885</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.5753715515000288</v>
+        <v>0.5729617092985411</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.503116164841813</v>
+        <v>0.5012767504635874</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.4563231405067678</v>
+        <v>0.4550246586400593</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>244.1076183349406</v>
+        <v>242.74167764639</v>
       </c>
       <c r="B12" t="n">
-        <v>258.6036666572045</v>
+        <v>257.0836111482484</v>
       </c>
       <c r="C12" t="n">
-        <v>73.64255457728426</v>
+        <v>73.57655425741854</v>
       </c>
       <c r="D12" t="n">
-        <v>175.2798986071072</v>
+        <v>173.954118159576</v>
       </c>
       <c r="E12" t="n">
-        <v>77.13848332444941</v>
+        <v>77.00051877139516</v>
       </c>
       <c r="F12" t="n">
-        <v>272.195612650739</v>
+        <v>270.6761821760063</v>
       </c>
       <c r="G12" t="n">
-        <v>299.2797740508382</v>
+        <v>297.6484864069328</v>
       </c>
       <c r="H12" t="n">
-        <v>280.339973264828</v>
+        <v>278.7751512911255</v>
       </c>
       <c r="I12" t="n">
-        <v>124.018629427381</v>
+        <v>124.8073993224185</v>
       </c>
       <c r="J12" t="n">
-        <v>119.80199602685</v>
+        <v>120.6882618349</v>
       </c>
       <c r="K12" t="n">
-        <v>115.5218676633101</v>
+        <v>116.5036472257932</v>
       </c>
       <c r="L12" t="n">
-        <v>138.9087740857852</v>
+        <v>139.6502048261157</v>
       </c>
       <c r="M12" t="n">
-        <v>1.034946378902684</v>
+        <v>1.038117776037218</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5995590344082492</v>
+        <v>0.6065484697360168</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9820515447644864</v>
+        <v>0.9867771985390752</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6289652326690253</v>
+        <v>0.635637215156942</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.9630885606881855</v>
+        <v>0.9676300269766744</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3341233280191602</v>
+        <v>0.3319928118197324</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3824925103562372</v>
+        <v>0.3802287288030584</v>
       </c>
       <c r="T12" t="n">
-        <v>297.6447106257144</v>
+        <v>295.9859272468424</v>
       </c>
       <c r="U12" t="n">
-        <v>297.6447106257144</v>
+        <v>295.9859272468424</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="X12" t="n">
-        <v>73.64255457728426</v>
+        <v>73.57655425741855</v>
       </c>
       <c r="Y12" t="n">
-        <v>175.2798986071072</v>
+        <v>173.954118159576</v>
       </c>
       <c r="Z12" t="n">
-        <v>77.1384833244494</v>
+        <v>77.00051877139515</v>
       </c>
       <c r="AA12" t="n">
-        <v>124.018629427381</v>
+        <v>124.8073993224185</v>
       </c>
       <c r="AB12" t="n">
-        <v>119.80199602685</v>
+        <v>120.6882618349</v>
       </c>
       <c r="AC12" t="n">
-        <v>115.5218676633101</v>
+        <v>116.5036472257932</v>
       </c>
       <c r="AD12" t="n">
-        <v>138.9087740857852</v>
+        <v>139.6502048261157</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.034946378902684</v>
+        <v>1.038117776037218</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.5995590344082491</v>
+        <v>0.6065484697360168</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.9820515447644865</v>
+        <v>0.9867771985390753</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.5056406331528392</v>
+        <v>0.5113714866167668</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.7748157043761672</v>
+        <v>0.7798628422959147</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.269175071223328</v>
+        <v>0.2684913556791479</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.3824925103562374</v>
+        <v>0.3802287288030585</v>
       </c>
       <c r="AL12" t="n">
-        <v>256.042157387004</v>
+        <v>255.0349311744851</v>
       </c>
       <c r="AM12" t="n">
-        <v>210.8054989959889</v>
+        <v>210.2230384539992</v>
       </c>
       <c r="AN12" t="n">
-        <v>171.247380921188</v>
+        <v>171.6316374502103</v>
       </c>
       <c r="AO12" t="n">
-        <v>145.9293273269078</v>
+        <v>146.5474979291121</v>
       </c>
       <c r="AP12" t="n">
-        <v>510.9001254982634</v>
+        <v>510.8639593128875</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.5011589244322358</v>
+        <v>0.4992227901876407</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.544450223835763</v>
+        <v>0.5423084494402666</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.4854417239453542</v>
+        <v>0.4837776197916482</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.4482586082130921</v>
+        <v>0.447020059156569</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>256.4716257365505</v>
+        <v>255.0330751975033</v>
       </c>
       <c r="B13" t="n">
-        <v>263.8600148310113</v>
+        <v>262.3423856154226</v>
       </c>
       <c r="C13" t="n">
-        <v>77.13848332444941</v>
+        <v>77.00051877139516</v>
       </c>
       <c r="D13" t="n">
-        <v>182.1598513072502</v>
+        <v>180.8443140361741</v>
       </c>
       <c r="E13" t="n">
-        <v>81.41288214658081</v>
+        <v>81.1570012761472</v>
       </c>
       <c r="F13" t="n">
-        <v>277.7343710361876</v>
+        <v>276.1803282196052</v>
       </c>
       <c r="G13" t="n">
-        <v>299.2797740508382</v>
+        <v>297.6484864069328</v>
       </c>
       <c r="H13" t="n">
-        <v>282.8735630363536</v>
+        <v>281.3109846524458</v>
       </c>
       <c r="I13" t="n">
-        <v>115.5218676633101</v>
+        <v>116.5036472257932</v>
       </c>
       <c r="J13" t="n">
-        <v>111.3075506026314</v>
+        <v>112.3868234664391</v>
       </c>
       <c r="K13" t="n">
-        <v>107.0343712586483</v>
+        <v>108.2091500418257</v>
       </c>
       <c r="L13" t="n">
-        <v>134.4783031204187</v>
+        <v>135.2615207991944</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9820515447644864</v>
+        <v>0.9867771985390752</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5485000041227774</v>
+        <v>0.5560469181028412</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9205306330924201</v>
+        <v>0.9272943973999979</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5722691779916664</v>
+        <v>0.579458777075661</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9376116433351077</v>
+        <v>0.9433853511439693</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3653424653434413</v>
+        <v>0.3639265740683083</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3720306289696427</v>
+        <v>0.3712474792971566</v>
       </c>
       <c r="T13" t="n">
-        <v>297.4812042832021</v>
+        <v>295.8196713308334</v>
       </c>
       <c r="U13" t="n">
-        <v>297.4812042832021</v>
+        <v>295.8196713308334</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="X13" t="n">
-        <v>77.1384833244494</v>
+        <v>77.00051877139515</v>
       </c>
       <c r="Y13" t="n">
-        <v>182.1598513072502</v>
+        <v>180.8443140361741</v>
       </c>
       <c r="Z13" t="n">
-        <v>81.4128821465808</v>
+        <v>81.15700127614718</v>
       </c>
       <c r="AA13" t="n">
-        <v>115.5218676633101</v>
+        <v>116.5036472257932</v>
       </c>
       <c r="AB13" t="n">
-        <v>111.3075506026314</v>
+        <v>112.3868234664391</v>
       </c>
       <c r="AC13" t="n">
-        <v>107.0343712586483</v>
+        <v>108.2091500418257</v>
       </c>
       <c r="AD13" t="n">
-        <v>134.4783031204187</v>
+        <v>135.2615207991944</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.9820515447644865</v>
+        <v>0.9867771985390753</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.5485000041227773</v>
+        <v>0.5560469181028412</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.9205306330924201</v>
+        <v>0.927294397399998</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.4828844909217589</v>
+        <v>0.4892458202226391</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.7676891125614371</v>
+        <v>0.7740135875346763</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.2848046216396782</v>
+        <v>0.2847677673120372</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.3720306289696428</v>
+        <v>0.3712474792971567</v>
       </c>
       <c r="AL13" t="n">
-        <v>248.7895025677854</v>
+        <v>247.9010313486872</v>
       </c>
       <c r="AM13" t="n">
-        <v>213.3205988080342</v>
+        <v>212.7644024843617</v>
       </c>
       <c r="AN13" t="n">
-        <v>160.2759659879217</v>
+        <v>160.7797589061233</v>
       </c>
       <c r="AO13" t="n">
-        <v>138.0734860172896</v>
+        <v>138.8262718652808</v>
       </c>
       <c r="AP13" t="n">
-        <v>525.6508995026371</v>
+        <v>525.6121767940765</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.4732979679159424</v>
+        <v>0.4716424814598797</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.5147278062660953</v>
+        <v>0.5128896224327064</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.4691213550751291</v>
+        <v>0.4676623389367524</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.4413451641751344</v>
+        <v>0.4401944334948509</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>268.8218943254603</v>
+        <v>267.310503520026</v>
       </c>
       <c r="B14" t="n">
-        <v>269.6494260505675</v>
+        <v>268.1245494211836</v>
       </c>
       <c r="C14" t="n">
-        <v>81.41288214658081</v>
+        <v>81.1570012761472</v>
       </c>
       <c r="D14" t="n">
-        <v>188.7745730407151</v>
+        <v>187.5120535285802</v>
       </c>
       <c r="E14" t="n">
-        <v>81.41288214658081</v>
+        <v>81.1570012761472</v>
       </c>
       <c r="F14" t="n">
-        <v>283.4281429017593</v>
+        <v>281.8384708823306</v>
       </c>
       <c r="G14" t="n">
-        <v>299.2797740508382</v>
+        <v>297.6484864069328</v>
       </c>
       <c r="H14" t="n">
-        <v>285.6939249283784</v>
+        <v>284.1292908039491</v>
       </c>
       <c r="I14" t="n">
-        <v>107.0343712586483</v>
+        <v>108.2091500418257</v>
       </c>
       <c r="J14" t="n">
-        <v>107.0343712586483</v>
+        <v>108.2091500418257</v>
       </c>
       <c r="K14" t="n">
-        <v>107.0343712586483</v>
+        <v>108.2091500418257</v>
       </c>
       <c r="L14" t="n">
-        <v>134.4783031204187</v>
+        <v>135.2615207991944</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9205306330924201</v>
+        <v>0.9272943973999979</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5157980306420287</v>
+        <v>0.5233948265415658</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9205306330924201</v>
+        <v>0.9272943973999979</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5189188442645907</v>
+        <v>0.5265484555843728</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9237227319161456</v>
+        <v>0.9305226414849395</v>
       </c>
       <c r="R14" t="n">
-        <v>0.404803887651555</v>
+        <v>0.4039741859005667</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4047326024503914</v>
+        <v>0.4038995708584321</v>
       </c>
       <c r="T14" t="n">
-        <v>297.3176979406897</v>
+        <v>295.6534154148244</v>
       </c>
       <c r="U14" t="n">
-        <v>297.3176979406897</v>
+        <v>295.6534154148244</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6646305405713923</v>
+        <v>0.6610078313788489</v>
       </c>
       <c r="X14" t="n">
-        <v>81.4128821465808</v>
+        <v>81.15700127614718</v>
       </c>
       <c r="Y14" t="n">
-        <v>188.7745730407151</v>
+        <v>187.5120535285802</v>
       </c>
       <c r="Z14" t="n">
-        <v>81.4128821465808</v>
+        <v>81.15700127614718</v>
       </c>
       <c r="AA14" t="n">
-        <v>107.0343712586483</v>
+        <v>108.2091500418257</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.0343712586483</v>
+        <v>108.2091500418257</v>
       </c>
       <c r="AC14" t="n">
-        <v>107.0343712586483</v>
+        <v>108.2091500418257</v>
       </c>
       <c r="AD14" t="n">
-        <v>134.4783031204187</v>
+        <v>135.2615207991944</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.9205306330924201</v>
+        <v>0.927294397399998</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.5157980306420287</v>
+        <v>0.5233948265415658</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.9205306330924201</v>
+        <v>0.927294397399998</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.4602401920838452</v>
+        <v>0.467225179119906</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.7783996174666783</v>
+        <v>0.7857114889946889</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.3181594253828331</v>
+        <v>0.3184863098747829</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.4047326024503914</v>
+        <v>0.4038995708584322</v>
       </c>
       <c r="AL14" t="n">
-        <v>240.9797628719521</v>
+        <v>240.2455656846246</v>
       </c>
       <c r="AM14" t="n">
-        <v>215.8205144943306</v>
+        <v>215.3191736711716</v>
       </c>
       <c r="AN14" t="n">
-        <v>152.4400426193382</v>
+        <v>152.9829216069101</v>
       </c>
       <c r="AO14" t="n">
-        <v>134.1532648879608</v>
+        <v>134.9355203303021</v>
       </c>
       <c r="AP14" t="n">
-        <v>539.9485925578826</v>
+        <v>539.9102080210085</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.446301307556643</v>
+        <v>0.4449731864956263</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.485784368564147</v>
+        <v>0.4843043209751012</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.4537749285124847</v>
+        <v>0.4525686123743858</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.4350665429633071</v>
+        <v>0.434055904010429</v>
       </c>
     </row>
   </sheetData>
